--- a/base.xlsx
+++ b/base.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC DELL DES URBANO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4536AD57-7A32-4CF7-9466-AE9EEDD6215B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C662F91-9478-4665-BC92-89C5218D190E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="98">
   <si>
     <t>Nombre completo</t>
   </si>
@@ -311,6 +324,9 @@
   </si>
   <si>
     <t>NUMERO DE EMPLEADO</t>
+  </si>
+  <si>
+    <t>CRUZ PAT LIAN VADHIR</t>
   </si>
 </sst>
 </file>
@@ -466,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -480,7 +496,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -501,58 +516,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="7">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF1E395B"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE69138"/>
-          <bgColor rgb="FFE69138"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thick">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thick">
-          <color rgb="FF000000"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Montserrat"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -657,16 +620,68 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thick">
           <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF1E395B"/>
+        <name val="Montserrat"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE69138"/>
+          <bgColor rgb="FFE69138"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thick">
           <color rgb="FF000000"/>
-        </bottom>
+        </left>
+        <right style="thick">
+          <color rgb="FF000000"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -683,12 +698,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B40D847-676B-4216-85D9-A46182724F19}" name="Tabla1" displayName="Tabla1" ref="A1:C84" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" headerRowBorderDxfId="5" tableBorderDxfId="6">
-  <autoFilter ref="A1:C84" xr:uid="{3B40D847-676B-4216-85D9-A46182724F19}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3B40D847-676B-4216-85D9-A46182724F19}" name="Tabla1" displayName="Tabla1" ref="A1:C85" totalsRowShown="0" headerRowDxfId="6" dataDxfId="4" headerRowBorderDxfId="5" tableBorderDxfId="3">
+  <autoFilter ref="A1:C85" xr:uid="{3B40D847-676B-4216-85D9-A46182724F19}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{534A4B2B-2B65-49CE-B445-6D03D4E60BB4}" name="NUMERO DE EMPLEADO" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{5D580D2E-606C-4BCF-8990-4498F46E4EE6}" name="Nombre completo" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{4F0B43BA-AF1A-47F3-A1F2-7A55279510CE}" name="Puesto" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{534A4B2B-2B65-49CE-B445-6D03D4E60BB4}" name="NUMERO DE EMPLEADO" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{5D580D2E-606C-4BCF-8990-4498F46E4EE6}" name="Nombre completo" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4F0B43BA-AF1A-47F3-A1F2-7A55279510CE}" name="Puesto" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -895,7 +910,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1006,7 +1021,7 @@
       <c r="A10" s="4">
         <v>4906</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -1014,42 +1029,44 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>7664</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
+      <c r="A12" s="3">
+        <v>2031</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
         <v>9602</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>6676</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>6059</v>
+        <v>6676</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>5</v>
@@ -1057,76 +1074,76 @@
     </row>
     <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
+        <v>6059</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>7288</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>9173</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>8869</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
+        <v>8869</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>8917</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="C19" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>7909</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>3508</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>3934</v>
+        <v>3508</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
@@ -1134,21 +1151,21 @@
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>5553</v>
+        <v>3934</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>5625</v>
+        <v>5553</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>12</v>
@@ -1156,10 +1173,10 @@
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>6081</v>
+        <v>5625</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>12</v>
@@ -1167,10 +1184,10 @@
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>8170</v>
+        <v>6081</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>12</v>
@@ -1178,10 +1195,10 @@
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>8397</v>
+        <v>8170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>12</v>
@@ -1189,120 +1206,120 @@
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>4891</v>
+        <v>8397</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
+        <v>4891</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>8429</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>8979</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>8824</v>
+        <v>8979</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
+      <c r="A31" s="2">
+        <v>8824</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>7725</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>8325</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>5434</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>8066</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
-        <v>3272</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>3943</v>
+        <v>3272</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>5685</v>
+        <v>3943</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>5</v>
@@ -1310,87 +1327,87 @@
     </row>
     <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>5728</v>
+        <v>5685</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>5992</v>
+        <v>5728</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>7023</v>
+        <v>5992</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
+        <v>7023</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>7166</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="C42" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>8497</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3">
-        <v>9634</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>3552</v>
+        <v>9634</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>4010</v>
+        <v>3552</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>5</v>
@@ -1398,10 +1415,10 @@
     </row>
     <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>4482</v>
+        <v>4010</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>5</v>
@@ -1409,10 +1426,10 @@
     </row>
     <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>4893</v>
+        <v>4482</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>5</v>
@@ -1420,219 +1437,219 @@
     </row>
     <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
+        <v>4893</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>4978</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="C49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
         <v>8323</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="3">
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>5020</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
         <v>7875</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3">
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>8546</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
-        <v>7932</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>58</v>
+      <c r="C53" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
+        <v>7932</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
         <v>8888</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3">
-        <v>9648</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>3087</v>
+        <v>9648</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>4071</v>
+        <v>3087</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>4463</v>
+        <v>4071</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>8730</v>
+        <v>4463</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
+        <v>8730</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>8915</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+    <row r="62" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
         <v>7436</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3">
-        <v>4982</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>5906</v>
+        <v>4982</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
+        <v>5906</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>7021</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B65" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+    <row r="66" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
         <v>8679</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B66" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C66" s="2" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="3">
-        <v>598</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>4026</v>
+        <v>598</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>51</v>
@@ -1640,10 +1657,10 @@
     </row>
     <row r="68" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>4341</v>
+        <v>4026</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>51</v>
@@ -1651,10 +1668,10 @@
     </row>
     <row r="69" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>5394</v>
+        <v>4341</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>51</v>
@@ -1662,10 +1679,10 @@
     </row>
     <row r="70" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>5900</v>
+        <v>5394</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>51</v>
@@ -1673,10 +1690,10 @@
     </row>
     <row r="71" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>6421</v>
+        <v>5900</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>51</v>
@@ -1684,10 +1701,10 @@
     </row>
     <row r="72" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>6544</v>
+        <v>6421</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>51</v>
@@ -1695,43 +1712,43 @@
     </row>
     <row r="73" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>6681</v>
+        <v>6544</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
+        <v>6681</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
         <v>8801</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A75" s="3">
-        <v>2309</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>4189</v>
+        <v>2309</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>51</v>
@@ -1739,10 +1756,10 @@
     </row>
     <row r="77" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>4247</v>
+        <v>4189</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>51</v>
@@ -1750,10 +1767,10 @@
     </row>
     <row r="78" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>6189</v>
+        <v>4247</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>51</v>
@@ -1761,10 +1778,10 @@
     </row>
     <row r="79" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>6353</v>
+        <v>6189</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>51</v>
@@ -1772,10 +1789,10 @@
     </row>
     <row r="80" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>6598</v>
+        <v>6353</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>51</v>
@@ -1783,45 +1800,56 @@
     </row>
     <row r="81" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>7132</v>
+        <v>6598</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>7435</v>
+        <v>7132</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
+        <v>7435</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>8591</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B84" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+    <row r="85" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="9">
         <v>8430</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C85" s="9" t="s">
         <v>5</v>
       </c>
     </row>
